--- a/annotation/Species_list_vs_CATAMI_2023_06.xlsx
+++ b/annotation/Species_list_vs_CATAMI_2023_06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9F119C-04BD-4A85-A841-D4963FCE2DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60CE492-B78E-499C-A366-8A168F6B1C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13770" yWindow="-18120" windowWidth="29040" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER_naming" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="498">
   <si>
     <t>Label</t>
   </si>
@@ -992,9 +992,6 @@
     <t>Sipuncula</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -1488,6 +1485,36 @@
   </si>
   <si>
     <t>Exclude_img</t>
+  </si>
+  <si>
+    <t>Final_labels_img</t>
+  </si>
+  <si>
+    <t>Final_labels_2km</t>
+  </si>
+  <si>
+    <t>Final_labels_500m</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension Feeders Buried</t>
+  </si>
+  <si>
+    <t>Hydrozoa - Soft</t>
+  </si>
+  <si>
+    <t>Octocorals - Branching - Non-fleshy - Bottlebrush</t>
+  </si>
+  <si>
+    <t>Octocorals - 3D - Non-Fleshy</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple -Other</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Ball</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Other</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1582,12 +1609,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1615,422 +1643,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2412,13 +2024,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
@@ -2427,15 +2039,18 @@
     <col min="10" max="10" width="5.33203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="17.33203125" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" style="5" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" customWidth="1"/>
+    <col min="13" max="13" width="50" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.21875" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="19" max="19" width="70.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2470,10 +2085,10 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>10</v>
@@ -2488,10 +2103,19 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2522,8 +2146,11 @@
       <c r="O2">
         <v>7.5999999999999998E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2534,7 +2161,7 @@
         <v>1E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>221</v>
@@ -2557,8 +2184,11 @@
       <c r="O3" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -2569,7 +2199,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>223</v>
@@ -2589,8 +2219,11 @@
       <c r="O4">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2601,7 +2234,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E5" s="3"/>
       <c r="G5" s="3"/>
@@ -2617,8 +2250,11 @@
       <c r="O5">
         <v>0.17599999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2629,7 +2265,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>223</v>
@@ -2661,8 +2297,11 @@
       <c r="Q6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2673,7 +2312,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>225</v>
@@ -2696,8 +2335,11 @@
       <c r="O7">
         <v>9.8000000000000004E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S7" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2708,7 +2350,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>225</v>
@@ -2737,8 +2379,11 @@
       <c r="O8">
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2749,7 +2394,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>225</v>
@@ -2772,8 +2417,11 @@
       <c r="O9">
         <v>3.9E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2784,7 +2432,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>225</v>
@@ -2807,8 +2455,11 @@
       <c r="O10">
         <v>8.3000000000000004E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2819,7 +2470,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>225</v>
@@ -2842,8 +2493,11 @@
       <c r="O11">
         <v>0.35899999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2854,7 +2508,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>225</v>
@@ -2877,8 +2531,11 @@
       <c r="O12">
         <v>0.159</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S12" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2904,10 +2561,10 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -2916,10 +2573,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2930,13 +2590,13 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G14" s="3">
         <v>20000908</v>
@@ -2953,8 +2613,11 @@
       <c r="O14">
         <v>0.32200000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S14" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2965,13 +2628,13 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G15" s="3">
         <v>20000908</v>
@@ -2988,8 +2651,11 @@
       <c r="O15">
         <v>4.1000000000000002E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S15" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -3000,13 +2666,13 @@
         <v>0.114</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G16" s="3">
         <v>20000908</v>
@@ -3023,8 +2689,11 @@
       <c r="O16">
         <v>0.27900000000000003</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S16" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3035,13 +2704,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G17" s="3">
         <v>20000908</v>
@@ -3067,8 +2736,11 @@
       <c r="Q17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S17" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -3079,13 +2751,13 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G18" s="3">
         <v>20000902</v>
@@ -3102,8 +2774,11 @@
       <c r="O18">
         <v>0.153</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S18" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3114,13 +2789,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G19" s="3">
         <v>20000903</v>
@@ -3137,8 +2812,11 @@
       <c r="O19">
         <v>0.111</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S19" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -3149,13 +2827,13 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G20" s="3">
         <v>20000904</v>
@@ -3172,8 +2850,11 @@
       <c r="O20">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S20" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3184,7 +2865,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>230</v>
@@ -3207,8 +2888,11 @@
       <c r="O21">
         <v>6.8000000000000005E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S21" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3219,13 +2903,13 @@
         <v>1.6E-2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G22" s="3">
         <v>20000908</v>
@@ -3242,8 +2926,11 @@
       <c r="O22">
         <v>4.3999999999999997E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S22" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -3254,13 +2941,13 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G23" s="3">
         <v>20000906</v>
@@ -3277,8 +2964,11 @@
       <c r="O23">
         <v>0.23100000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S23" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -3289,7 +2979,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>230</v>
@@ -3312,8 +3002,11 @@
       <c r="O24">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S24" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -3324,13 +3017,13 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>230</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G25" s="3">
         <v>20000907</v>
@@ -3347,8 +3040,11 @@
       <c r="O25">
         <v>0.17899999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S25" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -3379,8 +3075,11 @@
       <c r="O26" s="4">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S26" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -3391,7 +3090,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>151</v>
@@ -3406,10 +3105,10 @@
         <v>1.6E-2</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N27">
         <v>13</v>
@@ -3418,10 +3117,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3432,7 +3134,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>151</v>
@@ -3450,10 +3152,10 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -3462,10 +3164,13 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3476,7 +3181,7 @@
         <v>1E-3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>151</v>
@@ -3491,10 +3196,10 @@
         <v>2E-3</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -3503,10 +3208,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3517,7 +3225,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>151</v>
@@ -3532,10 +3240,10 @@
         <v>2.7E-2</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N30">
         <v>23</v>
@@ -3544,10 +3252,13 @@
         <v>0.05</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3558,7 +3269,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>151</v>
@@ -3576,10 +3287,10 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N31">
         <v>73</v>
@@ -3588,10 +3299,13 @@
         <v>0.159</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -3602,7 +3316,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>237</v>
@@ -3620,10 +3334,10 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N32">
         <v>68</v>
@@ -3632,10 +3346,13 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -3646,7 +3363,7 @@
         <v>1E-3</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>237</v>
@@ -3664,13 +3381,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K33" t="s">
         <v>43</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s">
         <v>43</v>
@@ -3682,13 +3399,16 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q33" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S33" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -3699,7 +3419,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>237</v>
@@ -3717,10 +3437,10 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N34">
         <v>23</v>
@@ -3729,10 +3449,13 @@
         <v>0.05</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3743,13 +3466,13 @@
         <v>2E-3</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G35" s="3">
         <v>25001901</v>
@@ -3760,11 +3483,9 @@
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="J35" s="6"/>
       <c r="L35" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -3772,14 +3493,15 @@
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="P35" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="P35" s="8"/>
       <c r="R35" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -3790,13 +3512,13 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G36" s="3">
         <v>25001902</v>
@@ -3808,10 +3530,10 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N36">
         <v>138</v>
@@ -3820,10 +3542,13 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -3834,13 +3559,13 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G37" s="3">
         <v>25200902</v>
@@ -3852,10 +3577,10 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N37">
         <v>45</v>
@@ -3864,10 +3589,13 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -3878,13 +3606,13 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G38" s="3">
         <v>25200901</v>
@@ -3896,10 +3624,10 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N38">
         <v>24</v>
@@ -3908,10 +3636,13 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -3922,13 +3653,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G39" s="3">
         <v>25200901</v>
@@ -3940,10 +3671,10 @@
         <v>4.7E-2</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N39">
         <v>38</v>
@@ -3952,10 +3683,13 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3966,13 +3700,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G40" s="3">
         <v>25400901</v>
@@ -3984,13 +3718,13 @@
         <v>1.2E-2</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K40" t="s">
         <v>52</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s">
         <v>52</v>
@@ -4002,13 +3736,16 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q40" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S40" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -4019,13 +3756,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G41" s="3">
         <v>25400901</v>
@@ -4037,10 +3774,10 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N41">
         <v>70</v>
@@ -4049,10 +3786,13 @@
         <v>0.153</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -4063,13 +3803,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G42" s="3">
         <v>25400901</v>
@@ -4081,10 +3821,10 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N42">
         <v>44</v>
@@ -4093,10 +3833,13 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -4107,13 +3850,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G43" s="3">
         <v>25400901</v>
@@ -4125,10 +3868,10 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N43">
         <v>8</v>
@@ -4137,10 +3880,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -4151,13 +3897,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G44" s="3">
         <v>25400901</v>
@@ -4169,13 +3915,13 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K44" t="s">
         <v>54</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s">
         <v>54</v>
@@ -4187,13 +3933,16 @@
         <v>3.9E-2</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q44" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S44" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -4204,7 +3953,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>237</v>
@@ -4222,10 +3971,10 @@
         <v>2.3E-2</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N45">
         <v>14</v>
@@ -4234,10 +3983,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -4248,7 +4000,7 @@
         <v>1E-3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>237</v>
@@ -4265,11 +4017,9 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="J46" s="6"/>
       <c r="L46" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -4277,14 +4027,15 @@
       <c r="O46">
         <v>0</v>
       </c>
-      <c r="P46" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="P46" s="8"/>
       <c r="R46" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -4295,7 +4046,7 @@
         <v>0.252</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>237</v>
@@ -4313,10 +4064,10 @@
         <v>0.47299999999999998</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N47">
         <v>258</v>
@@ -4325,10 +4076,13 @@
         <v>0.56200000000000006</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -4339,7 +4093,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>237</v>
@@ -4357,10 +4111,10 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N48">
         <v>85</v>
@@ -4369,10 +4123,13 @@
         <v>0.185</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -4383,7 +4140,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>237</v>
@@ -4401,10 +4158,10 @@
         <v>0.02</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N49">
         <v>14</v>
@@ -4413,10 +4170,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -4445,10 +4205,10 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N50">
         <v>77</v>
@@ -4457,10 +4217,13 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -4494,8 +4257,11 @@
       <c r="O51">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S51" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -4516,10 +4282,10 @@
         <v>2E-3</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N52">
         <v>2</v>
@@ -4528,10 +4294,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -4562,8 +4331,11 @@
       <c r="O53">
         <v>0.20300000000000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S53" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -4584,10 +4356,10 @@
         <v>2E-3</v>
       </c>
       <c r="K54" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M54" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N54">
         <v>2</v>
@@ -4596,10 +4368,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="Q54" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="S54" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -4633,8 +4408,11 @@
       <c r="O55">
         <v>0.192</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S55" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -4645,7 +4423,7 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>248</v>
@@ -4665,8 +4443,11 @@
       <c r="O56">
         <v>0.185</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S56" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -4677,7 +4458,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>248</v>
@@ -4692,10 +4473,10 @@
         <v>1.6E-2</v>
       </c>
       <c r="K57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N57">
         <v>10</v>
@@ -4704,10 +4485,13 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="Q57" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -4728,10 +4512,10 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="K58" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M58" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N58">
         <v>8</v>
@@ -4740,10 +4524,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="Q58" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="S58" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -4769,13 +4556,13 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K59" t="s">
         <v>70</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M59" t="s">
         <v>70</v>
@@ -4787,13 +4574,16 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P59" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q59" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S59" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>71</v>
       </c>
@@ -4810,7 +4600,7 @@
         <v>70</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G60" s="3">
         <v>11000901</v>
@@ -4822,13 +4612,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K60" t="s">
         <v>70</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M60" t="s">
         <v>70</v>
@@ -4840,13 +4630,16 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="P60" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q60" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S60" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>72</v>
       </c>
@@ -4863,7 +4656,7 @@
         <v>70</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G61" s="3">
         <v>12000000</v>
@@ -4875,13 +4668,13 @@
         <v>2E-3</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K61" t="s">
         <v>70</v>
       </c>
       <c r="L61" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M61" t="s">
         <v>70</v>
@@ -4893,13 +4686,16 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q61" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S61" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>73</v>
       </c>
@@ -4910,7 +4706,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>256</v>
@@ -4928,13 +4724,13 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K62" t="s">
         <v>256</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M62" t="s">
         <v>256</v>
@@ -4946,10 +4742,13 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="P62" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S62" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4960,7 +4759,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>256</v>
@@ -4978,13 +4777,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K63" t="s">
         <v>256</v>
       </c>
       <c r="L63" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M63" t="s">
         <v>256</v>
@@ -4996,10 +4795,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="P63" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S63" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>75</v>
       </c>
@@ -5010,7 +4812,7 @@
         <v>1E-3</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>256</v>
@@ -5028,13 +4830,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K64" t="s">
         <v>256</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M64" t="s">
         <v>256</v>
@@ -5046,10 +4848,13 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="P64" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>76</v>
       </c>
@@ -5060,7 +4865,7 @@
         <v>1E-3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>256</v>
@@ -5078,13 +4883,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K65" t="s">
         <v>256</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M65" t="s">
         <v>256</v>
@@ -5096,13 +4901,16 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P65" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q65" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="S65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -5113,7 +4921,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>256</v>
@@ -5131,13 +4939,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K66" t="s">
         <v>256</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M66" t="s">
         <v>256</v>
@@ -5149,13 +4957,16 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="P66" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q66" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="S66" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>78</v>
       </c>
@@ -5166,7 +4977,7 @@
         <v>1E-3</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>256</v>
@@ -5184,13 +4995,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K67" t="s">
         <v>256</v>
       </c>
       <c r="L67" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M67" t="s">
         <v>256</v>
@@ -5202,13 +5013,16 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q67" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="S67" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -5243,8 +5057,11 @@
       <c r="Q68" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S68" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>80</v>
       </c>
@@ -5279,8 +5096,11 @@
       <c r="Q69" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S69" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -5315,8 +5135,11 @@
       <c r="Q70" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S70" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -5351,8 +5174,11 @@
       <c r="Q71" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S71" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -5378,8 +5204,11 @@
       <c r="O72">
         <v>0.126</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S72" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -5414,8 +5243,11 @@
       <c r="Q73" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S73" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -5450,8 +5282,11 @@
       <c r="Q74" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S74" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -5486,8 +5321,11 @@
       <c r="Q75" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S75" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -5498,7 +5336,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>269</v>
@@ -5521,8 +5359,11 @@
       <c r="O76">
         <v>5.7000000000000002E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S76" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -5533,7 +5374,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D77" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>269</v>
@@ -5565,8 +5406,11 @@
       <c r="Q77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S77" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -5577,13 +5421,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G78" s="3">
         <v>11168907</v>
@@ -5595,10 +5439,10 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K78" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M78" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N78">
         <v>13</v>
@@ -5606,8 +5450,11 @@
       <c r="O78">
         <v>2.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S78" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -5618,13 +5465,13 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G79" s="3">
         <v>11168906</v>
@@ -5636,10 +5483,10 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="K79" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M79" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N79">
         <v>116</v>
@@ -5647,8 +5494,11 @@
       <c r="O79">
         <v>0.253</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S79" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -5659,7 +5509,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D80" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>269</v>
@@ -5688,8 +5538,11 @@
       <c r="Q80" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S80" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -5700,13 +5553,13 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D81" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G81" s="3">
         <v>11168911</v>
@@ -5723,8 +5576,11 @@
       <c r="O81">
         <v>3.9E-2</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S81" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -5735,13 +5591,13 @@
         <v>1.9E-2</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G82" s="3">
         <v>11168910</v>
@@ -5758,8 +5614,11 @@
       <c r="O82">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S82" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -5770,13 +5629,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D83" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G83" s="3">
         <v>11168904</v>
@@ -5788,10 +5647,10 @@
         <v>1.2E-2</v>
       </c>
       <c r="K83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N83">
         <v>12</v>
@@ -5800,10 +5659,13 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="Q83" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+      <c r="S83" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -5814,13 +5676,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D84" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G84" s="3">
         <v>11168903</v>
@@ -5832,10 +5694,10 @@
         <v>1.2E-2</v>
       </c>
       <c r="K84" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M84" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N84">
         <v>9</v>
@@ -5844,10 +5706,13 @@
         <v>0.02</v>
       </c>
       <c r="Q84" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+      <c r="S84" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -5858,7 +5723,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>269</v>
@@ -5881,8 +5746,11 @@
       <c r="O85">
         <v>4.1000000000000002E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S85" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -5913,8 +5781,11 @@
       <c r="O86">
         <v>6.0999999999999999E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S86" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -5925,7 +5796,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>269</v>
@@ -5948,8 +5819,11 @@
       <c r="O87">
         <v>0.14399999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S87" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -5975,10 +5849,10 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L88" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N88">
         <v>53</v>
@@ -5987,10 +5861,13 @@
         <v>0.115</v>
       </c>
       <c r="P88" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -6019,10 +5896,10 @@
         <v>1E-3</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L89" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -6031,10 +5908,13 @@
         <v>2E-3</v>
       </c>
       <c r="P89" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S89" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -6045,13 +5925,13 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G90" s="3">
         <v>10000904</v>
@@ -6068,8 +5948,11 @@
       <c r="O90">
         <v>0.27900000000000003</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S90" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -6080,13 +5963,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G91" s="3">
         <v>10000904</v>
@@ -6112,8 +5995,11 @@
       <c r="Q91" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S91" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -6124,13 +6010,13 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G92" s="3">
         <v>10000904</v>
@@ -6147,8 +6033,11 @@
       <c r="O92">
         <v>0.14799999999999999</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S92" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -6159,13 +6048,13 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G93" s="3">
         <v>10000904</v>
@@ -6185,8 +6074,11 @@
       <c r="O93">
         <v>5.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S93" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -6197,13 +6089,13 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G94" s="3">
         <v>10000905</v>
@@ -6220,8 +6112,11 @@
       <c r="O94">
         <v>0.17599999999999999</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S94" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -6232,13 +6127,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G95" s="3">
         <v>10000905</v>
@@ -6258,8 +6153,11 @@
       <c r="O95">
         <v>3.6999999999999998E-2</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S95" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -6270,13 +6168,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G96" s="3">
         <v>10000907</v>
@@ -6293,8 +6191,11 @@
       <c r="O96">
         <v>9.4E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S96" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -6305,13 +6206,13 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G97" s="3">
         <v>10000907</v>
@@ -6328,8 +6229,11 @@
       <c r="O97">
         <v>0.14199999999999999</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S97" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -6340,7 +6244,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>277</v>
@@ -6369,8 +6273,11 @@
       <c r="Q98" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S98" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -6381,13 +6288,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G99" s="3">
         <v>10000915</v>
@@ -6404,8 +6311,11 @@
       <c r="O99">
         <v>7.3999999999999996E-2</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S99" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>111</v>
       </c>
@@ -6416,7 +6326,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>277</v>
@@ -6439,8 +6349,11 @@
       <c r="O100">
         <v>8.1000000000000003E-2</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S100" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>112</v>
       </c>
@@ -6451,13 +6364,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G101" s="3">
         <v>10000919</v>
@@ -6483,8 +6396,11 @@
       <c r="Q101" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S101" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>113</v>
       </c>
@@ -6495,13 +6411,13 @@
         <v>0.01</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G102" s="3">
         <v>10000920</v>
@@ -6518,8 +6434,11 @@
       <c r="O102">
         <v>5.8999999999999997E-2</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S102" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -6530,13 +6449,13 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G103" s="3">
         <v>10000902</v>
@@ -6553,8 +6472,11 @@
       <c r="O103">
         <v>0.26400000000000001</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S103" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>115</v>
       </c>
@@ -6565,7 +6487,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>277</v>
@@ -6583,10 +6505,10 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="K104" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M104" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N104">
         <v>10</v>
@@ -6594,8 +6516,11 @@
       <c r="O104">
         <v>2.1999999999999999E-2</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S104" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>116</v>
       </c>
@@ -6606,13 +6531,13 @@
         <v>2.7E-2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G105" s="3">
         <v>10000915</v>
@@ -6629,8 +6554,11 @@
       <c r="O105">
         <v>8.6999999999999994E-2</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S105" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>117</v>
       </c>
@@ -6641,13 +6569,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G106" s="3">
         <v>10000913</v>
@@ -6664,8 +6592,11 @@
       <c r="O106">
         <v>9.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S106" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>118</v>
       </c>
@@ -6676,13 +6607,13 @@
         <v>2E-3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G107" s="3">
         <v>10000914</v>
@@ -6708,8 +6639,11 @@
       <c r="Q107" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S107" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>119</v>
       </c>
@@ -6720,13 +6654,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G108" s="3">
         <v>10000916</v>
@@ -6738,10 +6672,10 @@
         <v>1.2E-2</v>
       </c>
       <c r="K108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N108">
         <v>11</v>
@@ -6749,8 +6683,11 @@
       <c r="O108">
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S108" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>120</v>
       </c>
@@ -6761,13 +6698,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G109" s="3">
         <v>10000906</v>
@@ -6779,10 +6716,10 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N109">
         <v>10</v>
@@ -6790,8 +6727,11 @@
       <c r="O109">
         <v>2.1999999999999999E-2</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S109" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>121</v>
       </c>
@@ -6802,13 +6742,13 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G110" s="3">
         <v>10000904</v>
@@ -6825,8 +6765,11 @@
       <c r="O110">
         <v>0.14599999999999999</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S110" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>122</v>
       </c>
@@ -6837,13 +6780,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G111" s="3">
         <v>10000904</v>
@@ -6860,8 +6803,11 @@
       <c r="O111">
         <v>6.8000000000000005E-2</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S111" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>123</v>
       </c>
@@ -6872,13 +6818,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G112" s="3">
         <v>10000911</v>
@@ -6895,8 +6841,11 @@
       <c r="O112">
         <v>6.5000000000000002E-2</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S112" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>124</v>
       </c>
@@ -6922,8 +6871,11 @@
       <c r="O113">
         <v>6.3E-2</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S113" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>125</v>
       </c>
@@ -6949,8 +6901,11 @@
       <c r="O114">
         <v>9.8000000000000004E-2</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S114" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>126</v>
       </c>
@@ -6984,8 +6939,11 @@
       <c r="O115">
         <v>9.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S115" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>127</v>
       </c>
@@ -7019,8 +6977,11 @@
       <c r="O116">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S116" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>128</v>
       </c>
@@ -7060,8 +7021,11 @@
       <c r="O117">
         <v>3.3000000000000002E-2</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S117" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>129</v>
       </c>
@@ -7095,8 +7059,11 @@
       <c r="O118">
         <v>0.29399999999999998</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S118" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -7130,8 +7097,11 @@
       <c r="O119">
         <v>0.20300000000000001</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S119" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>131</v>
       </c>
@@ -7165,8 +7135,11 @@
       <c r="O120">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S120" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>132</v>
       </c>
@@ -7200,8 +7173,11 @@
       <c r="O121">
         <v>0.82799999999999996</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S121" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>133</v>
       </c>
@@ -7235,8 +7211,11 @@
       <c r="O122">
         <v>0.74099999999999999</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S122" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>134</v>
       </c>
@@ -7270,8 +7249,11 @@
       <c r="O123">
         <v>0.107</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S123" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>135</v>
       </c>
@@ -7297,8 +7279,11 @@
       <c r="O124">
         <v>0.41599999999999998</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S124" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>136</v>
       </c>
@@ -7324,8 +7309,11 @@
       <c r="O125">
         <v>9.6000000000000002E-2</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S125" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>137</v>
       </c>
@@ -7351,8 +7339,11 @@
       <c r="O126">
         <v>0.33600000000000002</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S126" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -7378,8 +7369,11 @@
       <c r="O127">
         <v>0.224</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S127" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -7405,8 +7399,11 @@
       <c r="O128">
         <v>0.52500000000000002</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S128" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>140</v>
       </c>
@@ -7432,8 +7429,11 @@
       <c r="O129">
         <v>0.745</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S129" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -7459,13 +7459,13 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K130" t="s">
         <v>143</v>
       </c>
       <c r="L130" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M130" t="s">
         <v>143</v>
@@ -7477,13 +7477,16 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P130" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q130" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S130" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>142</v>
       </c>
@@ -7509,10 +7512,10 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L131" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N131">
         <v>153</v>
@@ -7521,10 +7524,13 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="P131" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S131" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>143</v>
       </c>
@@ -7550,10 +7556,10 @@
         <v>0.03</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N132">
         <v>27</v>
@@ -7562,10 +7568,13 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="P132" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S132" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>144</v>
       </c>
@@ -7576,7 +7585,7 @@
         <v>2E-3</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>208</v>
@@ -7594,13 +7603,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K133" t="s">
         <v>143</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M133" t="s">
         <v>143</v>
@@ -7612,13 +7621,16 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="P133" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q133" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S133" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>145</v>
       </c>
@@ -7629,7 +7641,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>208</v>
@@ -7647,10 +7659,10 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N134">
         <v>39</v>
@@ -7659,10 +7671,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="P134" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S134" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>146</v>
       </c>
@@ -7673,7 +7688,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>208</v>
@@ -7691,10 +7706,10 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="J135" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N135">
         <v>73</v>
@@ -7703,10 +7718,13 @@
         <v>0.159</v>
       </c>
       <c r="P135" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S135" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>147</v>
       </c>
@@ -7717,7 +7735,7 @@
         <v>1E-3</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>208</v>
@@ -7732,13 +7750,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K136" t="s">
         <v>143</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M136" t="s">
         <v>143</v>
@@ -7750,13 +7768,16 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="P136" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q136" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S136" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>148</v>
       </c>
@@ -7767,7 +7788,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>208</v>
@@ -7785,10 +7806,10 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="J137" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N137">
         <v>200</v>
@@ -7797,10 +7818,13 @@
         <v>0.436</v>
       </c>
       <c r="P137" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="S137" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>149</v>
       </c>
@@ -7811,7 +7835,7 @@
         <v>2E-3</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>208</v>
@@ -7826,13 +7850,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K138" t="s">
         <v>143</v>
       </c>
       <c r="L138" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M138" t="s">
         <v>143</v>
@@ -7844,47 +7868,51 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="P138" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q138" t="s">
         <v>143</v>
       </c>
+      <c r="S138" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I138">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O138">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C138">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="40.77734375" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
@@ -7893,15 +7921,16 @@
     <col min="10" max="10" width="5.5546875" style="5" customWidth="1"/>
     <col min="11" max="11" width="23.77734375" customWidth="1"/>
     <col min="12" max="12" width="8.33203125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="23.77734375" customWidth="1"/>
+    <col min="13" max="13" width="37.21875" customWidth="1"/>
     <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.21875" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="73.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7936,10 +7965,10 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>10</v>
@@ -7954,10 +7983,13 @@
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -7988,8 +8020,11 @@
       <c r="O2">
         <v>0.14199999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -8020,8 +8055,11 @@
       <c r="O3">
         <v>9.7000000000000003E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -8032,7 +8070,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>151</v>
@@ -8052,8 +8090,11 @@
       <c r="O4">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -8064,7 +8105,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>151</v>
@@ -8084,8 +8125,11 @@
       <c r="O5">
         <v>7.1999999999999995E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -8096,7 +8140,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>151</v>
@@ -8119,8 +8163,11 @@
       <c r="O6">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>155</v>
       </c>
@@ -8131,7 +8178,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>151</v>
@@ -8151,8 +8198,11 @@
       <c r="O7">
         <v>0.11700000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S7" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -8163,7 +8213,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>151</v>
@@ -8183,8 +8233,11 @@
       <c r="O8">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>157</v>
       </c>
@@ -8195,7 +8248,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>151</v>
@@ -8215,8 +8268,11 @@
       <c r="O9">
         <v>2.3E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -8227,7 +8283,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>151</v>
@@ -8247,8 +8303,11 @@
       <c r="O10">
         <v>0.23599999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>159</v>
       </c>
@@ -8259,7 +8318,7 @@
         <v>1E-3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>151</v>
@@ -8282,8 +8341,11 @@
       <c r="O11">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>160</v>
       </c>
@@ -8294,7 +8356,7 @@
         <v>0.53300000000000003</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>151</v>
@@ -8317,8 +8379,11 @@
       <c r="O12">
         <v>0.68500000000000005</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S12" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -8329,7 +8394,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>237</v>
@@ -8352,8 +8417,11 @@
       <c r="O13">
         <v>0.11700000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S13" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -8364,7 +8432,7 @@
         <v>2E-3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>237</v>
@@ -8381,9 +8449,7 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="J14" s="8"/>
       <c r="L14"/>
       <c r="N14">
         <v>0</v>
@@ -8391,14 +8457,15 @@
       <c r="O14">
         <v>0</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="P14" s="8"/>
       <c r="R14" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>163</v>
       </c>
@@ -8409,7 +8476,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>237</v>
@@ -8441,8 +8508,11 @@
       <c r="Q15" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S15" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -8453,7 +8523,7 @@
         <v>0.90800000000000003</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>237</v>
@@ -8476,8 +8546,11 @@
       <c r="O16">
         <v>0.96599999999999997</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S16" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>165</v>
       </c>
@@ -8488,7 +8561,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>237</v>
@@ -8511,8 +8584,11 @@
       <c r="O17">
         <v>0.14199999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S17" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>166</v>
       </c>
@@ -8523,7 +8599,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>237</v>
@@ -8546,8 +8622,11 @@
       <c r="O18">
         <v>0.46400000000000002</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S18" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>167</v>
       </c>
@@ -8558,7 +8637,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>237</v>
@@ -8581,8 +8660,11 @@
       <c r="O19">
         <v>0.16900000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S19" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -8593,7 +8675,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>237</v>
@@ -8616,8 +8698,11 @@
       <c r="O20">
         <v>3.2000000000000001E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S20" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -8628,7 +8713,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>237</v>
@@ -8651,8 +8736,11 @@
       <c r="O21">
         <v>8.3000000000000004E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S21" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -8663,7 +8751,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>237</v>
@@ -8686,8 +8774,11 @@
       <c r="O22">
         <v>3.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S22" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>171</v>
       </c>
@@ -8698,7 +8789,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>237</v>
@@ -8721,8 +8812,11 @@
       <c r="O23">
         <v>6.5000000000000002E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S23" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>172</v>
       </c>
@@ -8733,13 +8827,13 @@
         <v>2.3E-2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G24" s="3">
         <v>25001901</v>
@@ -8756,8 +8850,11 @@
       <c r="O24">
         <v>5.6000000000000001E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S24" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>173</v>
       </c>
@@ -8768,13 +8865,13 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G25" s="3">
         <v>25001902</v>
@@ -8791,8 +8888,11 @@
       <c r="O25">
         <v>0.45700000000000002</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S25" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -8803,13 +8903,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G26" s="3">
         <v>25400901</v>
@@ -8826,8 +8926,11 @@
       <c r="O26">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S26" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>175</v>
       </c>
@@ -8838,13 +8941,13 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G27" s="3">
         <v>25400901</v>
@@ -8861,8 +8964,11 @@
       <c r="O27">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S27" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>176</v>
       </c>
@@ -8873,13 +8979,13 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G28" s="3">
         <v>25400901</v>
@@ -8896,8 +9002,11 @@
       <c r="O28">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S28" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>177</v>
       </c>
@@ -8908,13 +9017,13 @@
         <v>3.9E-2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G29" s="3">
         <v>25400901</v>
@@ -8931,8 +9040,11 @@
       <c r="O29">
         <v>0.113</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S29" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>178</v>
       </c>
@@ -8943,13 +9055,13 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G30" s="3">
         <v>25400901</v>
@@ -8966,8 +9078,11 @@
       <c r="O30">
         <v>7.9000000000000001E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S30" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>179</v>
       </c>
@@ -8978,7 +9093,7 @@
         <v>0.378</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>237</v>
@@ -9001,8 +9116,11 @@
       <c r="O31">
         <v>0.58799999999999997</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S31" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>180</v>
       </c>
@@ -9013,7 +9131,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>237</v>
@@ -9036,8 +9154,11 @@
       <c r="O32">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S32" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>181</v>
       </c>
@@ -9048,7 +9169,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>237</v>
@@ -9080,8 +9201,11 @@
       <c r="Q33" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S33" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>182</v>
       </c>
@@ -9092,7 +9216,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>237</v>
@@ -9115,8 +9239,11 @@
       <c r="O34">
         <v>4.7E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S34" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>183</v>
       </c>
@@ -9127,7 +9254,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>237</v>
@@ -9150,8 +9277,11 @@
       <c r="O35">
         <v>9.9000000000000005E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S35" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>184</v>
       </c>
@@ -9162,13 +9292,13 @@
         <v>0.12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G36" s="3">
         <v>25200902</v>
@@ -9185,8 +9315,11 @@
       <c r="O36">
         <v>0.24299999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S36" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -9197,13 +9330,13 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G37" s="3">
         <v>25200901</v>
@@ -9220,8 +9353,11 @@
       <c r="O37">
         <v>0.27900000000000003</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S37" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>186</v>
       </c>
@@ -9232,13 +9368,13 @@
         <v>0.156</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>237</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G38" s="3">
         <v>25200901</v>
@@ -9255,8 +9391,11 @@
       <c r="O38">
         <v>0.26600000000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S38" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>187</v>
       </c>
@@ -9290,8 +9429,11 @@
       <c r="O39">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S39" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -9325,8 +9467,11 @@
       <c r="O40">
         <v>7.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S40" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>70</v>
       </c>
@@ -9357,8 +9502,11 @@
       <c r="O41">
         <v>5.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S41" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>189</v>
       </c>
@@ -9389,8 +9537,11 @@
       <c r="O42">
         <v>3.4000000000000002E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S42" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -9421,8 +9572,11 @@
       <c r="O43">
         <v>6.3E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S43" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>190</v>
       </c>
@@ -9447,9 +9601,7 @@
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="J44" s="8"/>
       <c r="L44"/>
       <c r="N44">
         <v>0</v>
@@ -9457,14 +9609,15 @@
       <c r="O44">
         <v>0</v>
       </c>
-      <c r="P44" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="P44" s="8"/>
       <c r="R44" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -9475,7 +9628,7 @@
         <v>0.01</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>256</v>
@@ -9498,8 +9651,11 @@
       <c r="O45">
         <v>3.5999999999999997E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S45" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>192</v>
       </c>
@@ -9510,7 +9666,7 @@
         <v>0.03</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>256</v>
@@ -9533,8 +9689,11 @@
       <c r="O46">
         <v>0.113</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S46" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -9545,7 +9704,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>256</v>
@@ -9568,8 +9727,11 @@
       <c r="O47">
         <v>4.2999999999999997E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S47" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>194</v>
       </c>
@@ -9580,7 +9742,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>256</v>
@@ -9603,8 +9765,11 @@
       <c r="O48">
         <v>0.108</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S48" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>195</v>
       </c>
@@ -9615,7 +9780,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>256</v>
@@ -9638,8 +9803,11 @@
       <c r="O49">
         <v>0.28199999999999997</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S49" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>196</v>
       </c>
@@ -9650,7 +9818,7 @@
         <v>2E-3</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>256</v>
@@ -9682,8 +9850,11 @@
       <c r="Q50" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S50" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>197</v>
       </c>
@@ -9694,7 +9865,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>256</v>
@@ -9726,8 +9897,11 @@
       <c r="Q51" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S51" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>198</v>
       </c>
@@ -9738,7 +9912,7 @@
         <v>0.03</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>256</v>
@@ -9761,8 +9935,11 @@
       <c r="O52">
         <v>9.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S52" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>199</v>
       </c>
@@ -9773,7 +9950,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>256</v>
@@ -9796,8 +9973,11 @@
       <c r="O53">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S53" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -9823,8 +10003,11 @@
       <c r="O54">
         <v>0.69099999999999995</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S54" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>200</v>
       </c>
@@ -9859,8 +10042,11 @@
       <c r="Q55" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S55" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>201</v>
       </c>
@@ -9895,8 +10081,11 @@
       <c r="Q56" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S56" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>202</v>
       </c>
@@ -9931,8 +10120,11 @@
       <c r="Q57" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S57" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>203</v>
       </c>
@@ -9967,8 +10159,11 @@
       <c r="Q58" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S58" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>204</v>
       </c>
@@ -9994,8 +10189,11 @@
       <c r="O59">
         <v>0.27700000000000002</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S59" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>205</v>
       </c>
@@ -10030,8 +10228,11 @@
       <c r="Q60" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S60" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>206</v>
       </c>
@@ -10062,8 +10263,11 @@
       <c r="O61">
         <v>0.56799999999999995</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S61" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>207</v>
       </c>
@@ -10103,8 +10307,11 @@
       <c r="Q62" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S62" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -10138,8 +10345,11 @@
       <c r="O63">
         <v>5.6000000000000001E-2</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S63" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>208</v>
       </c>
@@ -10170,8 +10380,11 @@
       <c r="O64">
         <v>0.72699999999999998</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S64" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>209</v>
       </c>
@@ -10182,7 +10395,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>208</v>
@@ -10205,8 +10418,11 @@
       <c r="O65">
         <v>7.6999999999999999E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S65" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>210</v>
       </c>
@@ -10217,7 +10433,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>208</v>
@@ -10240,8 +10456,11 @@
       <c r="O66">
         <v>0.108</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S66" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>211</v>
       </c>
@@ -10252,7 +10471,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>208</v>
@@ -10272,8 +10491,11 @@
       <c r="O67">
         <v>3.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S67" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>212</v>
       </c>
@@ -10304,8 +10526,11 @@
       <c r="O68">
         <v>0.14599999999999999</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S68" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>213</v>
       </c>
@@ -10342,8 +10567,11 @@
       <c r="O69">
         <v>2.9000000000000001E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S69" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>214</v>
       </c>
@@ -10374,8 +10602,11 @@
       <c r="O70">
         <v>3.2000000000000001E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S70" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>215</v>
       </c>
@@ -10386,7 +10617,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>208</v>
@@ -10406,8 +10637,11 @@
       <c r="O71">
         <v>5.3999999999999999E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S71" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>216</v>
       </c>
@@ -10418,7 +10652,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>208</v>
@@ -10435,20 +10669,17 @@
       <c r="I72">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="K72" t="s">
-        <v>212</v>
-      </c>
-      <c r="M72" t="s">
-        <v>212</v>
-      </c>
       <c r="N72">
         <v>9</v>
       </c>
       <c r="O72">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S72" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>217</v>
       </c>
@@ -10459,7 +10690,7 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>208</v>
@@ -10482,8 +10713,11 @@
       <c r="O73">
         <v>0.182</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S73" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>218</v>
       </c>
@@ -10494,7 +10728,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>208</v>
@@ -10517,8 +10751,11 @@
       <c r="O74">
         <v>7.3999999999999996E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S74" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>219</v>
       </c>
@@ -10529,7 +10766,7 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>208</v>
@@ -10552,8 +10789,11 @@
       <c r="O75">
         <v>0.376</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="S75" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>220</v>
       </c>
@@ -10564,7 +10804,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>208</v>
@@ -10587,15 +10827,18 @@
       <c r="O76">
         <v>6.8000000000000005E-2</v>
       </c>
+      <c r="S76" s="2" t="s">
+        <v>483</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I76">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O76">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0.02</formula>
     </cfRule>
   </conditionalFormatting>
